--- a/plantillas/plantilla_crear_estudiantes.xlsx
+++ b/plantillas/plantilla_crear_estudiantes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,27 +436,59 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>APELLIDOS</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>NOMBRES</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>GRADO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CURSO</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>APELLIDOS</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>NOMBRES</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CORREO_PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PEREZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>JUAN CAMILO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>juan.perez@gmail.com</t>
         </is>
       </c>
     </row>
